--- a/inspection_forms/005_shift_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/005_shift_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Employee Signature</t>
+          <t>Employee Signature (2)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>employee_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Employee 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>employee_choices</t>
+          <t>employee_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>employee_choices</t>
+          <t>employee_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
